--- a/backend/data/financials_by_company/000636.SZ.xlsx
+++ b/backend/data/financials_by_company/000636.SZ.xlsx
@@ -682,634 +682,634 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-11049959.361783</v>
+        <v>2147956.829</v>
       </c>
       <c r="C2" t="n">
-        <v>0.101045</v>
+        <v>0.118655</v>
       </c>
       <c r="D2" t="n">
-        <v>1106931235.46</v>
+        <v>1412888050.14</v>
       </c>
       <c r="E2" t="n">
-        <v>-109356758.27</v>
+        <v>18102492.42</v>
       </c>
       <c r="F2" t="n">
-        <v>-109356758.27</v>
+        <v>18102492.42</v>
       </c>
       <c r="G2" t="n">
-        <v>337368788.8</v>
+        <v>943116841.86</v>
       </c>
       <c r="H2" t="n">
-        <v>616451086.4299999</v>
+        <v>326121666.87</v>
       </c>
       <c r="I2" t="n">
-        <v>3992211249.67</v>
+        <v>3491448668.56</v>
       </c>
       <c r="J2" t="n">
-        <v>997574477.1900001</v>
+        <v>1430990542.56</v>
       </c>
       <c r="K2" t="n">
-        <v>381123390.76</v>
+        <v>1104868875.69</v>
       </c>
       <c r="L2" t="n">
-        <v>77391675.67</v>
+        <v>19650165.75</v>
       </c>
       <c r="M2" t="n">
-        <v>12976561.37</v>
+        <v>25946897.03</v>
       </c>
       <c r="N2" t="n">
-        <v>91529400.20999999</v>
+        <v>47612689.62</v>
       </c>
       <c r="O2" t="n">
-        <v>435675587.708217</v>
+        <v>927162306.2690001</v>
       </c>
       <c r="P2" t="n">
-        <v>337368788.8</v>
+        <v>943116841.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>4588910854.34</v>
+        <v>4132789658.86</v>
       </c>
       <c r="R2" t="n">
-        <v>390009762.41</v>
+        <v>1087798860.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1163340651</v>
+        <v>898206516</v>
       </c>
       <c r="T2" t="n">
-        <v>1163340651</v>
+        <v>898206516</v>
       </c>
       <c r="U2" t="n">
-        <v>0.29</v>
+        <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.29</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>337368788.8</v>
+        <v>943116841.86</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>337368788.8</v>
+        <v>943116841.86</v>
       </c>
       <c r="Z2" t="n">
-        <v>6421375.05</v>
+        <v>-7785316.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>330947413.75</v>
+        <v>950902158.0599999</v>
       </c>
       <c r="AB2" t="n">
-        <v>330947413.75</v>
+        <v>950902158.0599999</v>
       </c>
       <c r="AC2" t="n">
-        <v>37199415.64</v>
+        <v>128019820.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>368146829.39</v>
+        <v>1078921978.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>-21862933.02</v>
+        <v>-8876881.539999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>-109356758.27</v>
+        <v>18102492.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>-765686.03</v>
+        <v>-50631756.07</v>
       </c>
       <c r="AH2" t="n">
-        <v>36999925.91</v>
+        <v>91658.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>73122518.39</v>
+        <v>32437605.06</v>
       </c>
       <c r="AJ2" t="n">
-        <v>77391675.67</v>
+        <v>19650165.75</v>
       </c>
       <c r="AK2" t="n">
-        <v>1161163.17</v>
+        <v>2015626.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>12976561.37</v>
+        <v>25946897.03</v>
       </c>
       <c r="AM2" t="n">
-        <v>91529400.20999999</v>
+        <v>47612689.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>350335183.77</v>
+        <v>922270263.92</v>
       </c>
       <c r="AO2" t="n">
-        <v>596699604.67</v>
+        <v>641340990.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>41387808.91</v>
+        <v>49789008.51</v>
       </c>
       <c r="AQ2" t="n">
-        <v>42619819.57</v>
+        <v>30776138.35</v>
       </c>
       <c r="AR2" t="n">
-        <v>42619819.57</v>
+        <v>30776138.35</v>
       </c>
       <c r="AS2" t="n">
-        <v>240401749.26</v>
+        <v>245223646.95</v>
       </c>
       <c r="AT2" t="n">
-        <v>56457107.27</v>
+        <v>74302121.06</v>
       </c>
       <c r="AU2" t="n">
-        <v>16251215.83</v>
+        <v>15654116.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>40205891.44</v>
+        <v>58648004.86</v>
       </c>
       <c r="AW2" t="n">
-        <v>947034788.4400001</v>
+        <v>1563611254.22</v>
       </c>
       <c r="AX2" t="n">
-        <v>3992211249.67</v>
+        <v>3491448668.56</v>
       </c>
       <c r="AY2" t="n">
-        <v>4939246038.11</v>
+        <v>5055059922.78</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4939246038.11</v>
+        <v>5055059922.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-473577.411362</v>
+        <v>-1756147.942718</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01091</v>
+        <v>0.022266</v>
       </c>
       <c r="D3" t="n">
-        <v>735851346.9299999</v>
+        <v>884359434.41</v>
       </c>
       <c r="E3" t="n">
-        <v>-43406361.09</v>
+        <v>-78870544.41</v>
       </c>
       <c r="F3" t="n">
-        <v>-43406361.09</v>
+        <v>-78870544.41</v>
       </c>
       <c r="G3" t="n">
-        <v>173478853.85</v>
+        <v>327237346.74</v>
       </c>
       <c r="H3" t="n">
-        <v>497920655.13</v>
+        <v>428877492.75</v>
       </c>
       <c r="I3" t="n">
-        <v>3616353835.77</v>
+        <v>3177849230.31</v>
       </c>
       <c r="J3" t="n">
-        <v>692444985.84</v>
+        <v>805488890</v>
       </c>
       <c r="K3" t="n">
-        <v>194524330.71</v>
+        <v>376611397.25</v>
       </c>
       <c r="L3" t="n">
-        <v>131272438.64</v>
+        <v>123048207.89</v>
       </c>
       <c r="M3" t="n">
-        <v>11339706.81</v>
+        <v>29223660.71</v>
       </c>
       <c r="N3" t="n">
-        <v>143190016.91</v>
+        <v>152898023.71</v>
       </c>
       <c r="O3" t="n">
-        <v>216411637.528638</v>
+        <v>404351743.207282</v>
       </c>
       <c r="P3" t="n">
-        <v>173478853.85</v>
+        <v>327237346.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>4158044439.96</v>
+        <v>3728309565.79</v>
       </c>
       <c r="R3" t="n">
-        <v>207450831.08</v>
+        <v>327651803.74</v>
       </c>
       <c r="S3" t="n">
-        <v>1156525692</v>
+        <v>1055604344</v>
       </c>
       <c r="T3" t="n">
-        <v>1156525692</v>
+        <v>1055604344</v>
       </c>
       <c r="U3" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="V3" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="W3" t="n">
-        <v>173478853.85</v>
+        <v>327237346.74</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>173478853.85</v>
+        <v>327237346.74</v>
       </c>
       <c r="Z3" t="n">
-        <v>-7707166.67</v>
+        <v>-12415382.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>181186020.52</v>
+        <v>339652728.96</v>
       </c>
       <c r="AB3" t="n">
-        <v>181186020.52</v>
+        <v>339652728.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>1998603.38</v>
+        <v>7735007.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>183184623.9</v>
+        <v>347387736.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>-24266207.18</v>
+        <v>19735932.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>-44380316.61</v>
+        <v>-79049981.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5290208.14</v>
+        <v>-88532336.16</v>
       </c>
       <c r="AH3" t="n">
-        <v>17220981.13</v>
+        <v>30063850.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>32449543.62</v>
+        <v>137518467.39</v>
       </c>
       <c r="AJ3" t="n">
-        <v>131272438.64</v>
+        <v>123048207.89</v>
       </c>
       <c r="AK3" t="n">
-        <v>577871.46</v>
+        <v>626155.11</v>
       </c>
       <c r="AL3" t="n">
-        <v>11339706.81</v>
+        <v>29223660.71</v>
       </c>
       <c r="AM3" t="n">
-        <v>143190016.91</v>
+        <v>152898023.71</v>
       </c>
       <c r="AN3" t="n">
-        <v>63385083.29</v>
+        <v>145622429.98</v>
       </c>
       <c r="AO3" t="n">
-        <v>541690604.1900001</v>
+        <v>550460335.48</v>
       </c>
       <c r="AP3" t="n">
-        <v>33589910.73</v>
+        <v>33183255.17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>50644555.13</v>
+        <v>42458599.66</v>
       </c>
       <c r="AR3" t="n">
-        <v>50644555.13</v>
+        <v>42458599.66</v>
       </c>
       <c r="AS3" t="n">
-        <v>193099924.63</v>
+        <v>225330651.63</v>
       </c>
       <c r="AT3" t="n">
-        <v>66673801.49</v>
+        <v>59503915.15</v>
       </c>
       <c r="AU3" t="n">
-        <v>18584139.17</v>
+        <v>16059701.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>48089662.32</v>
+        <v>43444213.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>605075687.48</v>
+        <v>696082765.46</v>
       </c>
       <c r="AX3" t="n">
-        <v>3616353835.77</v>
+        <v>3177849230.31</v>
       </c>
       <c r="AY3" t="n">
-        <v>4221429523.25</v>
+        <v>3873931995.77</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4221429523.25</v>
+        <v>3873931995.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1756147.942718</v>
+        <v>-473577.411362</v>
       </c>
       <c r="C4" t="n">
-        <v>0.022266</v>
+        <v>0.01091</v>
       </c>
       <c r="D4" t="n">
-        <v>884359434.41</v>
+        <v>735851346.9299999</v>
       </c>
       <c r="E4" t="n">
-        <v>-78870544.41</v>
+        <v>-43406361.09</v>
       </c>
       <c r="F4" t="n">
-        <v>-78870544.41</v>
+        <v>-43406361.09</v>
       </c>
       <c r="G4" t="n">
-        <v>327237346.74</v>
+        <v>173478853.85</v>
       </c>
       <c r="H4" t="n">
-        <v>428877492.75</v>
+        <v>497920655.13</v>
       </c>
       <c r="I4" t="n">
-        <v>3177849230.31</v>
+        <v>3616353835.77</v>
       </c>
       <c r="J4" t="n">
-        <v>805488890</v>
+        <v>692444985.84</v>
       </c>
       <c r="K4" t="n">
-        <v>376611397.25</v>
+        <v>194524330.71</v>
       </c>
       <c r="L4" t="n">
-        <v>123048207.89</v>
+        <v>131272438.64</v>
       </c>
       <c r="M4" t="n">
-        <v>29223660.71</v>
+        <v>11339706.81</v>
       </c>
       <c r="N4" t="n">
-        <v>152898023.71</v>
+        <v>143190016.91</v>
       </c>
       <c r="O4" t="n">
-        <v>404351743.207282</v>
+        <v>216411637.528638</v>
       </c>
       <c r="P4" t="n">
-        <v>327237346.74</v>
+        <v>173478853.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>3728309565.79</v>
+        <v>4158044439.96</v>
       </c>
       <c r="R4" t="n">
-        <v>327651803.74</v>
+        <v>207450831.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1055604344</v>
+        <v>1156525692</v>
       </c>
       <c r="T4" t="n">
-        <v>1055604344</v>
+        <v>1156525692</v>
       </c>
       <c r="U4" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="W4" t="n">
-        <v>327237346.74</v>
+        <v>173478853.85</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>327237346.74</v>
+        <v>173478853.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>-12415382.22</v>
+        <v>-7707166.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>339652728.96</v>
+        <v>181186020.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>339652728.96</v>
+        <v>181186020.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>7735007.58</v>
+        <v>1998603.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>347387736.54</v>
+        <v>183184623.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>19735932.8</v>
+        <v>-24266207.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>-79049981.45</v>
+        <v>-44380316.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>-88532336.16</v>
+        <v>-5290208.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>30063850.22</v>
+        <v>17220981.13</v>
       </c>
       <c r="AI4" t="n">
-        <v>137518467.39</v>
+        <v>32449543.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>123048207.89</v>
+        <v>131272438.64</v>
       </c>
       <c r="AK4" t="n">
-        <v>626155.11</v>
+        <v>577871.46</v>
       </c>
       <c r="AL4" t="n">
-        <v>29223660.71</v>
+        <v>11339706.81</v>
       </c>
       <c r="AM4" t="n">
-        <v>152898023.71</v>
+        <v>143190016.91</v>
       </c>
       <c r="AN4" t="n">
-        <v>145622429.98</v>
+        <v>63385083.29</v>
       </c>
       <c r="AO4" t="n">
-        <v>550460335.48</v>
+        <v>541690604.1900001</v>
       </c>
       <c r="AP4" t="n">
-        <v>33183255.17</v>
+        <v>33589910.73</v>
       </c>
       <c r="AQ4" t="n">
-        <v>42458599.66</v>
+        <v>50644555.13</v>
       </c>
       <c r="AR4" t="n">
-        <v>42458599.66</v>
+        <v>50644555.13</v>
       </c>
       <c r="AS4" t="n">
-        <v>225330651.63</v>
+        <v>193099924.63</v>
       </c>
       <c r="AT4" t="n">
-        <v>59503915.15</v>
+        <v>66673801.49</v>
       </c>
       <c r="AU4" t="n">
-        <v>16059701.45</v>
+        <v>18584139.17</v>
       </c>
       <c r="AV4" t="n">
-        <v>43444213.7</v>
+        <v>48089662.32</v>
       </c>
       <c r="AW4" t="n">
-        <v>696082765.46</v>
+        <v>605075687.48</v>
       </c>
       <c r="AX4" t="n">
-        <v>3177849230.31</v>
+        <v>3616353835.77</v>
       </c>
       <c r="AY4" t="n">
-        <v>3873931995.77</v>
+        <v>4221429523.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3873931995.77</v>
+        <v>4221429523.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2147956.829</v>
+        <v>-11049959.361783</v>
       </c>
       <c r="C5" t="n">
-        <v>0.118655</v>
+        <v>0.101045</v>
       </c>
       <c r="D5" t="n">
-        <v>1412888050.14</v>
+        <v>1106931235.46</v>
       </c>
       <c r="E5" t="n">
-        <v>18102492.42</v>
+        <v>-109356758.27</v>
       </c>
       <c r="F5" t="n">
-        <v>18102492.42</v>
+        <v>-109356758.27</v>
       </c>
       <c r="G5" t="n">
-        <v>943116841.86</v>
+        <v>337368788.8</v>
       </c>
       <c r="H5" t="n">
-        <v>326121666.87</v>
+        <v>616451086.4299999</v>
       </c>
       <c r="I5" t="n">
-        <v>3491448668.56</v>
+        <v>3992211249.67</v>
       </c>
       <c r="J5" t="n">
-        <v>1430990542.56</v>
+        <v>997574477.1900001</v>
       </c>
       <c r="K5" t="n">
-        <v>1104868875.69</v>
+        <v>381123390.76</v>
       </c>
       <c r="L5" t="n">
-        <v>19650165.75</v>
+        <v>77391675.67</v>
       </c>
       <c r="M5" t="n">
-        <v>25946897.03</v>
+        <v>12976561.37</v>
       </c>
       <c r="N5" t="n">
-        <v>47612689.62</v>
+        <v>91529400.20999999</v>
       </c>
       <c r="O5" t="n">
-        <v>927162306.2690001</v>
+        <v>435675587.708217</v>
       </c>
       <c r="P5" t="n">
-        <v>943116841.86</v>
+        <v>337368788.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4132789658.86</v>
+        <v>4588910854.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1087798860.2</v>
+        <v>390009762.41</v>
       </c>
       <c r="S5" t="n">
-        <v>898206516</v>
+        <v>1163340651</v>
       </c>
       <c r="T5" t="n">
-        <v>898206516</v>
+        <v>1163340651</v>
       </c>
       <c r="U5" t="n">
-        <v>1.05</v>
+        <v>0.29</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0.29</v>
       </c>
       <c r="W5" t="n">
-        <v>943116841.86</v>
+        <v>337368788.8</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>943116841.86</v>
+        <v>337368788.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>-7785316.2</v>
+        <v>6421375.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>950902158.0599999</v>
+        <v>330947413.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>950902158.0599999</v>
+        <v>330947413.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>128019820.6</v>
+        <v>37199415.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>1078921978.66</v>
+        <v>368146829.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>-8876881.539999999</v>
+        <v>-21862933.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>18102492.42</v>
+        <v>-109356758.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>-50631756.07</v>
+        <v>-765686.03</v>
       </c>
       <c r="AH5" t="n">
-        <v>91658.59</v>
+        <v>36999925.91</v>
       </c>
       <c r="AI5" t="n">
-        <v>32437605.06</v>
+        <v>73122518.39</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19650165.75</v>
+        <v>77391675.67</v>
       </c>
       <c r="AK5" t="n">
-        <v>2015626.84</v>
+        <v>1161163.17</v>
       </c>
       <c r="AL5" t="n">
-        <v>25946897.03</v>
+        <v>12976561.37</v>
       </c>
       <c r="AM5" t="n">
-        <v>47612689.62</v>
+        <v>91529400.20999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>922270263.92</v>
+        <v>350335183.77</v>
       </c>
       <c r="AO5" t="n">
-        <v>641340990.3</v>
+        <v>596699604.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>49789008.51</v>
+        <v>41387808.91</v>
       </c>
       <c r="AQ5" t="n">
-        <v>30776138.35</v>
+        <v>42619819.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>30776138.35</v>
+        <v>42619819.57</v>
       </c>
       <c r="AS5" t="n">
-        <v>245223646.95</v>
+        <v>240401749.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>74302121.06</v>
+        <v>56457107.27</v>
       </c>
       <c r="AU5" t="n">
-        <v>15654116.2</v>
+        <v>16251215.83</v>
       </c>
       <c r="AV5" t="n">
-        <v>58648004.86</v>
+        <v>40205891.44</v>
       </c>
       <c r="AW5" t="n">
-        <v>1563611254.22</v>
+        <v>947034788.4400001</v>
       </c>
       <c r="AX5" t="n">
-        <v>3491448668.56</v>
+        <v>3992211249.67</v>
       </c>
       <c r="AY5" t="n">
-        <v>5055059922.78</v>
+        <v>4939246038.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5055059922.78</v>
+        <v>4939246038.11</v>
       </c>
     </row>
   </sheetData>
@@ -1690,88 +1690,216 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>895233111</v>
+      </c>
+      <c r="C2" t="n">
+        <v>895233111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1215570855.28</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6721718750.16</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8078442724.53</v>
+      </c>
+      <c r="G2" t="n">
+        <v>758751476.41</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6721718750.16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>51424198.65</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6948369420.15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7435411444.54</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7080387465.94</v>
+      </c>
+      <c r="M2" t="n">
+        <v>132018045.79</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6948369420.15</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>2794422125.53</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2414116225.76</v>
+      </c>
+      <c r="R2" t="n">
+        <v>895233111</v>
+      </c>
+      <c r="S2" t="n">
+        <v>895233111</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3747195020.39</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1042751563.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>15877144.54</v>
+      </c>
+      <c r="W2" t="n">
+        <v>251475381.33</v>
+      </c>
+      <c r="X2" t="n">
+        <v>192625236.21</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>44307578.29</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>538466223.04</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>51424198.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>487042024.39</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2704443456.98</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>259541480.78</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>677104632.24</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>643031279.99</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1752616292.16</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>415808549.47</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>25270362.98</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1311537379.71</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>10827582486.33</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>7364387552.94</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>425196492.97</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>148004256.25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>66366117.34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>718628499.1900001</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>718628499.1900001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>639996393.97</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17630674.91</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>226650669.99</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>226650669.99</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5121914448.32</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-2815063214.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7936977662.35</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1910664244.77</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>527923247.85</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4279083356.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1219306813.33</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3463194933.39</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>231605023.23</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>17301555.44</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>857816943.09</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="n">
-        <v>-185353294.36</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1724078819.44</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+      <c r="BJ2" t="n">
+        <v>419167627.21</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>280491416.86</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>158157899.02</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>371213128.32</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>778742523.76</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="n">
+        <v>1206515759.55</v>
+      </c>
       <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>1206515759.55</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>13471.83</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1205767523.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1157013211</v>
@@ -1780,43 +1908,43 @@
         <v>1157013211</v>
       </c>
       <c r="D3" t="n">
-        <v>476209578.51</v>
+        <v>1208512221.49</v>
       </c>
       <c r="E3" t="n">
-        <v>11951975788.59</v>
+        <v>11582965401.66</v>
       </c>
       <c r="F3" t="n">
-        <v>12361958521.97</v>
+        <v>12570752043.81</v>
       </c>
       <c r="G3" t="n">
-        <v>4438293024.89</v>
+        <v>4940664442.96</v>
       </c>
       <c r="H3" t="n">
-        <v>11951975788.59</v>
+        <v>11582965401.66</v>
       </c>
       <c r="I3" t="n">
-        <v>31913516.58</v>
+        <v>48465018.39</v>
       </c>
       <c r="J3" t="n">
-        <v>12222958521.97</v>
+        <v>11868848957.1</v>
       </c>
       <c r="K3" t="n">
-        <v>12361958521.97</v>
+        <v>12492621946.07</v>
       </c>
       <c r="L3" t="n">
-        <v>12367341760.24</v>
+        <v>12011392625.49</v>
       </c>
       <c r="M3" t="n">
-        <v>144383238.27</v>
+        <v>142543668.39</v>
       </c>
       <c r="N3" t="n">
-        <v>12222958521.97</v>
+        <v>11868848957.1</v>
       </c>
       <c r="O3" t="n">
-        <v>150026158.81</v>
+        <v>83678431.47</v>
       </c>
       <c r="P3" t="n">
-        <v>3167139322.68</v>
+        <v>2828324372.1</v>
       </c>
       <c r="Q3" t="n">
         <v>7123567658.62</v>
@@ -1828,162 +1956,160 @@
         <v>1157013211</v>
       </c>
       <c r="T3" t="n">
-        <v>3884865059.91</v>
+        <v>3814961443.51</v>
       </c>
       <c r="U3" t="n">
-        <v>489759919.18</v>
+        <v>971182104.14</v>
       </c>
       <c r="V3" t="n">
-        <v>4500000</v>
+        <v>27119664.45</v>
       </c>
       <c r="W3" t="n">
         <v>1454548</v>
       </c>
       <c r="X3" t="n">
-        <v>251801845.97</v>
+        <v>220932347.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>61090008.63</v>
+        <v>49437537.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>170913516.58</v>
+        <v>672238007.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>31913516.58</v>
+        <v>48465018.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>139000000</v>
+        <v>623772988.97</v>
       </c>
       <c r="AC3" t="n">
-        <v>3395105140.73</v>
+        <v>2843779339.37</v>
       </c>
       <c r="AD3" t="n">
-        <v>285159616.93</v>
+        <v>281528237.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>305296061.93</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>536274214.13</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>78130097.73999999</v>
+      </c>
       <c r="AG3" t="n">
-        <v>2790383713.53</v>
+        <v>2011035988.49</v>
       </c>
       <c r="AH3" t="n">
-        <v>372255498.74</v>
+        <v>283247918.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>18816783.99</v>
+        <v>14584817.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2399311430.8</v>
+        <v>1713203252.64</v>
       </c>
       <c r="AK3" t="n">
-        <v>16252206820.15</v>
+        <v>15826354069</v>
       </c>
       <c r="AL3" t="n">
-        <v>8418808654.53</v>
+        <v>8041910286.67</v>
       </c>
       <c r="AM3" t="n">
-        <v>82291549.06999999</v>
+        <v>71294329.90000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>156975190.49</v>
+        <v>150494008.64</v>
       </c>
       <c r="AO3" t="n">
-        <v>49284825.33</v>
+        <v>71046765.05</v>
       </c>
       <c r="AP3" t="n">
-        <v>1294651690.54</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>473989652.79</v>
-      </c>
+        <v>721391352.02</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>820662037.75</v>
+        <v>721391352.02</v>
       </c>
       <c r="AS3" t="n">
-        <v>749840318.45</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3069531.56</v>
-      </c>
+        <v>698654437.58</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>270982733.38</v>
+        <v>285883555.44</v>
       </c>
       <c r="AV3" t="n">
-        <v>270982733.38</v>
+        <v>285883555.44</v>
       </c>
       <c r="AW3" t="n">
-        <v>5811712815.71</v>
+        <v>6043145838.04</v>
       </c>
       <c r="AX3" t="n">
-        <v>-3781138554.75</v>
+        <v>-2774461694.96</v>
       </c>
       <c r="AY3" t="n">
-        <v>9592851370.459999</v>
+        <v>8817607533</v>
       </c>
       <c r="AZ3" t="n">
-        <v>150061447.86</v>
+        <v>1527875828.91</v>
       </c>
       <c r="BA3" t="n">
-        <v>825043974.11</v>
+        <v>831458022.66</v>
       </c>
       <c r="BB3" t="n">
-        <v>6669993962.03</v>
+        <v>4630207329.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>1947751986.46</v>
+        <v>1828066352.27</v>
       </c>
       <c r="BD3" t="n">
-        <v>7833398165.62</v>
+        <v>7784443782.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>153553504.49</v>
+        <v>88328382.95999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>39896488.84</v>
+        <v>13955482.02</v>
       </c>
       <c r="BG3" t="n">
-        <v>985232487.45</v>
+        <v>655869433.39</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
-      <c r="BI3" t="n">
-        <v>593088.8</v>
-      </c>
+      <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>373369627.2</v>
+        <v>319902787.94</v>
       </c>
       <c r="BK3" t="n">
-        <v>461536323.47</v>
+        <v>222732434.96</v>
       </c>
       <c r="BL3" t="n">
-        <v>149733447.98</v>
+        <v>113234210.49</v>
       </c>
       <c r="BM3" t="n">
-        <v>890401241.54</v>
+        <v>640082320.49</v>
       </c>
       <c r="BN3" t="n">
-        <v>1414911736.55</v>
+        <v>908735715.5700001</v>
       </c>
       <c r="BO3" t="n">
-        <v>-176812198.39</v>
+        <v>-176881838.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>1591723934.94</v>
+        <v>1085617553.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4349402706.75</v>
-      </c>
-      <c r="BR3" t="inlineStr"/>
+        <v>5477472447.9</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>118189635.16</v>
+      </c>
       <c r="BS3" t="n">
-        <v>4349402706.75</v>
+        <v>5359282812.74</v>
       </c>
       <c r="BT3" t="n">
-        <v>1025281.3</v>
+        <v>16777189.45</v>
       </c>
       <c r="BU3" t="n">
-        <v>4325465498.51</v>
+        <v>5328481854.96</v>
       </c>
     </row>
     <row r="4">
@@ -2207,7 +2333,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1157013211</v>
@@ -2216,43 +2342,43 @@
         <v>1157013211</v>
       </c>
       <c r="D5" t="n">
-        <v>1208512221.49</v>
+        <v>476209578.51</v>
       </c>
       <c r="E5" t="n">
-        <v>11582965401.66</v>
+        <v>11951975788.59</v>
       </c>
       <c r="F5" t="n">
-        <v>12570752043.81</v>
+        <v>12361958521.97</v>
       </c>
       <c r="G5" t="n">
-        <v>4940664442.96</v>
+        <v>4438293024.89</v>
       </c>
       <c r="H5" t="n">
-        <v>11582965401.66</v>
+        <v>11951975788.59</v>
       </c>
       <c r="I5" t="n">
-        <v>48465018.39</v>
+        <v>31913516.58</v>
       </c>
       <c r="J5" t="n">
-        <v>11868848957.1</v>
+        <v>12222958521.97</v>
       </c>
       <c r="K5" t="n">
-        <v>12492621946.07</v>
+        <v>12361958521.97</v>
       </c>
       <c r="L5" t="n">
-        <v>12011392625.49</v>
+        <v>12367341760.24</v>
       </c>
       <c r="M5" t="n">
-        <v>142543668.39</v>
+        <v>144383238.27</v>
       </c>
       <c r="N5" t="n">
-        <v>11868848957.1</v>
+        <v>12222958521.97</v>
       </c>
       <c r="O5" t="n">
-        <v>83678431.47</v>
+        <v>150026158.81</v>
       </c>
       <c r="P5" t="n">
-        <v>2828324372.1</v>
+        <v>3167139322.68</v>
       </c>
       <c r="Q5" t="n">
         <v>7123567658.62</v>
@@ -2264,370 +2390,244 @@
         <v>1157013211</v>
       </c>
       <c r="T5" t="n">
-        <v>3814961443.51</v>
+        <v>3884865059.91</v>
       </c>
       <c r="U5" t="n">
-        <v>971182104.14</v>
+        <v>489759919.18</v>
       </c>
       <c r="V5" t="n">
-        <v>27119664.45</v>
+        <v>4500000</v>
       </c>
       <c r="W5" t="n">
         <v>1454548</v>
       </c>
       <c r="X5" t="n">
-        <v>220932347.22</v>
+        <v>251801845.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>49437537.11</v>
+        <v>61090008.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>672238007.36</v>
+        <v>170913516.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>48465018.39</v>
+        <v>31913516.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>623772988.97</v>
+        <v>139000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2843779339.37</v>
+        <v>3395105140.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>281528237.52</v>
+        <v>285159616.93</v>
       </c>
       <c r="AE5" t="n">
-        <v>536274214.13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>78130097.73999999</v>
-      </c>
+        <v>305296061.93</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>2011035988.49</v>
+        <v>2790383713.53</v>
       </c>
       <c r="AH5" t="n">
-        <v>283247918.15</v>
+        <v>372255498.74</v>
       </c>
       <c r="AI5" t="n">
-        <v>14584817.7</v>
+        <v>18816783.99</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1713203252.64</v>
+        <v>2399311430.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>15826354069</v>
+        <v>16252206820.15</v>
       </c>
       <c r="AL5" t="n">
-        <v>8041910286.67</v>
+        <v>8418808654.53</v>
       </c>
       <c r="AM5" t="n">
-        <v>71294329.90000001</v>
+        <v>82291549.06999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>150494008.64</v>
+        <v>156975190.49</v>
       </c>
       <c r="AO5" t="n">
-        <v>71046765.05</v>
+        <v>49284825.33</v>
       </c>
       <c r="AP5" t="n">
-        <v>721391352.02</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>1294651690.54</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>473989652.79</v>
+      </c>
       <c r="AR5" t="n">
-        <v>721391352.02</v>
+        <v>820662037.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>698654437.58</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>749840318.45</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3069531.56</v>
+      </c>
       <c r="AU5" t="n">
-        <v>285883555.44</v>
+        <v>270982733.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>285883555.44</v>
+        <v>270982733.38</v>
       </c>
       <c r="AW5" t="n">
-        <v>6043145838.04</v>
+        <v>5811712815.71</v>
       </c>
       <c r="AX5" t="n">
-        <v>-2774461694.96</v>
+        <v>-3781138554.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>8817607533</v>
+        <v>9592851370.459999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1527875828.91</v>
+        <v>150061447.86</v>
       </c>
       <c r="BA5" t="n">
-        <v>831458022.66</v>
+        <v>825043974.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>4630207329.16</v>
+        <v>6669993962.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1828066352.27</v>
+        <v>1947751986.46</v>
       </c>
       <c r="BD5" t="n">
-        <v>7784443782.33</v>
+        <v>7833398165.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>88328382.95999999</v>
+        <v>153553504.49</v>
       </c>
       <c r="BF5" t="n">
-        <v>13955482.02</v>
+        <v>39896488.84</v>
       </c>
       <c r="BG5" t="n">
-        <v>655869433.39</v>
+        <v>985232487.45</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
-      <c r="BI5" t="inlineStr"/>
+      <c r="BI5" t="n">
+        <v>593088.8</v>
+      </c>
       <c r="BJ5" t="n">
-        <v>319902787.94</v>
+        <v>373369627.2</v>
       </c>
       <c r="BK5" t="n">
-        <v>222732434.96</v>
+        <v>461536323.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>113234210.49</v>
+        <v>149733447.98</v>
       </c>
       <c r="BM5" t="n">
-        <v>640082320.49</v>
+        <v>890401241.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>908735715.5700001</v>
+        <v>1414911736.55</v>
       </c>
       <c r="BO5" t="n">
-        <v>-176881838.25</v>
+        <v>-176812198.39</v>
       </c>
       <c r="BP5" t="n">
-        <v>1085617553.82</v>
+        <v>1591723934.94</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5477472447.9</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>118189635.16</v>
-      </c>
+        <v>4349402706.75</v>
+      </c>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>5359282812.74</v>
+        <v>4349402706.75</v>
       </c>
       <c r="BT5" t="n">
-        <v>16777189.45</v>
+        <v>1025281.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>5328481854.96</v>
+        <v>4325465498.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>895233111</v>
-      </c>
-      <c r="C6" t="n">
-        <v>895233111</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1215570855.28</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6721718750.16</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8078442724.53</v>
-      </c>
-      <c r="G6" t="n">
-        <v>758751476.41</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6721718750.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>51424198.65</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6948369420.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7435411444.54</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7080387465.94</v>
-      </c>
-      <c r="M6" t="n">
-        <v>132018045.79</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6948369420.15</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>2794422125.53</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2414116225.76</v>
-      </c>
-      <c r="R6" t="n">
-        <v>895233111</v>
-      </c>
-      <c r="S6" t="n">
-        <v>895233111</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3747195020.39</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1042751563.41</v>
-      </c>
-      <c r="V6" t="n">
-        <v>15877144.54</v>
-      </c>
-      <c r="W6" t="n">
-        <v>251475381.33</v>
-      </c>
-      <c r="X6" t="n">
-        <v>192625236.21</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>44307578.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>538466223.04</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>51424198.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>487042024.39</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2704443456.98</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>259541480.78</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>677104632.24</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>643031279.99</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1752616292.16</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>415808549.47</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>25270362.98</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1311537379.71</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>10827582486.33</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>7364387552.94</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>425196492.97</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>148004256.25</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>66366117.34</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>718628499.1900001</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>718628499.1900001</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>639996393.97</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>17630674.91</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>226650669.99</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>226650669.99</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5121914448.32</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-2815063214.03</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7936977662.35</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1910664244.77</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>527923247.85</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4279083356.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1219306813.33</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3463194933.39</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>231605023.23</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>17301555.44</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>857816943.09</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="n">
-        <v>419167627.21</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>280491416.86</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>158157899.02</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>371213128.32</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>778742523.76</v>
-      </c>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="n">
-        <v>1206515759.55</v>
-      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>-185353294.36</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1724078819.44</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="n">
-        <v>1206515759.55</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>13471.83</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1205767523.8</v>
-      </c>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2882,572 +2882,572 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>155297146.34</v>
+        <v>-1571442330.07</v>
       </c>
       <c r="C2" t="n">
-        <v>-35178777.53</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>-520964184.78</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1170294618.99</v>
+      </c>
       <c r="E2" t="n">
-        <v>-297483706.83</v>
+        <v>-2206144367.97</v>
       </c>
       <c r="F2" t="n">
-        <v>4326490779.81</v>
+        <v>1205780995.63</v>
       </c>
       <c r="G2" t="n">
-        <v>4249529974.51</v>
+        <v>1951850750.27</v>
       </c>
       <c r="H2" t="n">
-        <v>5470277.19</v>
+        <v>-1523748.42</v>
       </c>
       <c r="I2" t="n">
-        <v>71490528.11</v>
+        <v>-744546006.22</v>
       </c>
       <c r="J2" t="n">
-        <v>-110163148.69</v>
+        <v>637797692.3</v>
       </c>
       <c r="K2" t="n">
-        <v>-3370589.34</v>
+        <v>68752688.77</v>
       </c>
       <c r="L2" t="n">
-        <v>-67445941.81999999</v>
+        <v>-78486430.68000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-35178777.53</v>
+        <v>649330434.21</v>
       </c>
       <c r="N2" t="n">
-        <v>-35178777.53</v>
+        <v>649330434.21</v>
       </c>
       <c r="O2" t="n">
-        <v>-35178777.53</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>-520964184.78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1170294618.99</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-271127176.37</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-2017045736.42</v>
+      </c>
+      <c r="R2" t="n">
+        <v>89977546.31999999</v>
+      </c>
       <c r="S2" t="n">
-        <v>5228761.01</v>
+        <v>35163485.23</v>
       </c>
       <c r="T2" t="n">
-        <v>224228761.01</v>
+        <v>68048488.83</v>
       </c>
       <c r="U2" t="n">
-        <v>-219000000</v>
+        <v>-32885003.6</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-276355937.38</v>
+        <v>-2142186767.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>21127769.45</v>
+        <v>63957600</v>
       </c>
       <c r="Z2" t="n">
-        <v>-297483706.83</v>
+        <v>-2206144367.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>452780853.17</v>
+        <v>634702037.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>-588167051.3099999</v>
+        <v>-568734241.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>17124168.88</v>
+        <v>-1392298.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>215253323.1</v>
+        <v>-129699897.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>-354189916.82</v>
+        <v>-456273551.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>-466354626.47</v>
+        <v>18631506.45</v>
       </c>
       <c r="AG2" t="n">
-        <v>41806776.09</v>
+        <v>68754482.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>616451086.4299999</v>
+        <v>326121666.87</v>
       </c>
       <c r="AI2" t="n">
-        <v>15436939.76</v>
+        <v>8032620.82</v>
       </c>
       <c r="AJ2" t="n">
-        <v>601014146.67</v>
+        <v>318089046.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>-58126767.34</v>
+        <v>-124194909.24</v>
       </c>
       <c r="AL2" t="n">
-        <v>-253048.75</v>
+        <v>-50676382.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>330947413.75</v>
+        <v>950902158.0599999</v>
       </c>
       <c r="AN2" t="n">
-        <v>452780853.17</v>
+        <v>634702037.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>-181066459.06</v>
+        <v>-273929661.28</v>
       </c>
       <c r="AP2" t="n">
-        <v>-3964318422.28</v>
+        <v>-3312506972.09</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-187682535.04</v>
+        <v>-256101176.97</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1074252450.28</v>
+        <v>-1069809172.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2702383436.96</v>
+        <v>-1986596622.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>4598165734.51</v>
+        <v>4221138671.27</v>
       </c>
       <c r="AU2" t="n">
-        <v>263198722.54</v>
+        <v>364982469.07</v>
       </c>
       <c r="AV2" t="n">
-        <v>4334967011.97</v>
+        <v>3856156202.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>18471760.99</v>
+        <v>-218113496.56</v>
       </c>
       <c r="C3" t="n">
-        <v>-1619057289.84</v>
+        <v>-1168431890.82</v>
       </c>
       <c r="D3" t="n">
-        <v>965164345.34</v>
+        <v>834569754.01</v>
       </c>
       <c r="E3" t="n">
-        <v>-336427478.01</v>
+        <v>-733324742.77</v>
       </c>
       <c r="F3" t="n">
-        <v>4249529974.51</v>
+        <v>5345259044.41</v>
       </c>
       <c r="G3" t="n">
-        <v>5345259044.41</v>
+        <v>1205780995.63</v>
       </c>
       <c r="H3" t="n">
-        <v>3858778.05</v>
+        <v>7313045.86</v>
       </c>
       <c r="I3" t="n">
-        <v>-1099587847.95</v>
+        <v>4132165002.92</v>
       </c>
       <c r="J3" t="n">
-        <v>-890575843.83</v>
+        <v>4219630268.37</v>
       </c>
       <c r="K3" t="n">
-        <v>-76868802.06999999</v>
+        <v>4873338435.85</v>
       </c>
       <c r="L3" t="n">
-        <v>-155646257.26</v>
+        <v>-317762110.67</v>
       </c>
       <c r="M3" t="n">
-        <v>-653892944.5</v>
+        <v>-333862136.81</v>
       </c>
       <c r="N3" t="n">
-        <v>-653892944.5</v>
+        <v>-333862136.81</v>
       </c>
       <c r="O3" t="n">
-        <v>-1619057289.84</v>
+        <v>-1168431890.82</v>
       </c>
       <c r="P3" t="n">
-        <v>965164345.34</v>
+        <v>834569754.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>-563911243.12</v>
+        <v>-602676511.66</v>
       </c>
       <c r="R3" t="n">
-        <v>16802005.96</v>
+        <v>40000000</v>
       </c>
       <c r="S3" t="n">
-        <v>-385449363.05</v>
+        <v>-126017065.99</v>
       </c>
       <c r="T3" t="n">
-        <v>718250936.95</v>
+        <v>62495663.33</v>
       </c>
       <c r="U3" t="n">
-        <v>-1103700300</v>
+        <v>-188512729.32</v>
       </c>
       <c r="V3" t="n">
-        <v>129409650</v>
+        <v>87831050.09999999</v>
       </c>
       <c r="W3" t="n">
-        <v>129409650</v>
+        <v>87831050.09999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-324673536.03</v>
+        <v>-604490495.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>11753941.98</v>
+        <v>128834247</v>
       </c>
       <c r="Z3" t="n">
-        <v>-336427478.01</v>
+        <v>-733324742.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>354899239</v>
+        <v>515211246.21</v>
       </c>
       <c r="AB3" t="n">
-        <v>-367851973.99</v>
+        <v>-213656534.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>13767604.57</v>
+        <v>5313590.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>-33161906.92</v>
+        <v>-357859477.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>-44983277.37</v>
+        <v>130370407.84</v>
       </c>
       <c r="AF3" t="n">
-        <v>-303474394.27</v>
+        <v>8518944.300000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>48823209.92</v>
+        <v>58620765.03</v>
       </c>
       <c r="AH3" t="n">
-        <v>497920655.13</v>
+        <v>428877492.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>12957099.7</v>
+        <v>11795385.66</v>
       </c>
       <c r="AJ3" t="n">
-        <v>484963555.43</v>
+        <v>417082107.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>-49952416.01</v>
+        <v>-132769499.64</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4896781.32</v>
+        <v>-133096023.69</v>
       </c>
       <c r="AM3" t="n">
-        <v>181186020.52</v>
+        <v>339652728.96</v>
       </c>
       <c r="AN3" t="n">
-        <v>354899239</v>
+        <v>515211246.21</v>
       </c>
       <c r="AO3" t="n">
-        <v>-53015227.81</v>
+        <v>77146926.73</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3758598952.92</v>
+        <v>-2928041548.77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-268061972.6</v>
+        <v>-322826031.62</v>
       </c>
       <c r="AR3" t="n">
-        <v>-924909862.21</v>
+        <v>-1037722795.24</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2565627118.11</v>
+        <v>-1567492721.91</v>
       </c>
       <c r="AT3" t="n">
-        <v>4166513419.73</v>
+        <v>3366105868.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>382677150.91</v>
+        <v>461718809.12</v>
       </c>
       <c r="AV3" t="n">
-        <v>3783836268.82</v>
+        <v>2904387059.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-218113496.56</v>
+        <v>18471760.99</v>
       </c>
       <c r="C4" t="n">
-        <v>-1168431890.82</v>
+        <v>-1619057289.84</v>
       </c>
       <c r="D4" t="n">
-        <v>834569754.01</v>
+        <v>965164345.34</v>
       </c>
       <c r="E4" t="n">
-        <v>-733324742.77</v>
+        <v>-336427478.01</v>
       </c>
       <c r="F4" t="n">
+        <v>4249529974.51</v>
+      </c>
+      <c r="G4" t="n">
         <v>5345259044.41</v>
       </c>
-      <c r="G4" t="n">
-        <v>1205780995.63</v>
-      </c>
       <c r="H4" t="n">
-        <v>7313045.86</v>
+        <v>3858778.05</v>
       </c>
       <c r="I4" t="n">
-        <v>4132165002.92</v>
+        <v>-1099587847.95</v>
       </c>
       <c r="J4" t="n">
-        <v>4219630268.37</v>
+        <v>-890575843.83</v>
       </c>
       <c r="K4" t="n">
-        <v>4873338435.85</v>
+        <v>-76868802.06999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-317762110.67</v>
+        <v>-155646257.26</v>
       </c>
       <c r="M4" t="n">
-        <v>-333862136.81</v>
+        <v>-653892944.5</v>
       </c>
       <c r="N4" t="n">
-        <v>-333862136.81</v>
+        <v>-653892944.5</v>
       </c>
       <c r="O4" t="n">
-        <v>-1168431890.82</v>
+        <v>-1619057289.84</v>
       </c>
       <c r="P4" t="n">
-        <v>834569754.01</v>
+        <v>965164345.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>-602676511.66</v>
+        <v>-563911243.12</v>
       </c>
       <c r="R4" t="n">
-        <v>40000000</v>
+        <v>16802005.96</v>
       </c>
       <c r="S4" t="n">
-        <v>-126017065.99</v>
+        <v>-385449363.05</v>
       </c>
       <c r="T4" t="n">
-        <v>62495663.33</v>
+        <v>718250936.95</v>
       </c>
       <c r="U4" t="n">
-        <v>-188512729.32</v>
+        <v>-1103700300</v>
       </c>
       <c r="V4" t="n">
-        <v>87831050.09999999</v>
+        <v>129409650</v>
       </c>
       <c r="W4" t="n">
-        <v>87831050.09999999</v>
+        <v>129409650</v>
       </c>
       <c r="X4" t="n">
-        <v>-604490495.77</v>
+        <v>-324673536.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>128834247</v>
+        <v>11753941.98</v>
       </c>
       <c r="Z4" t="n">
-        <v>-733324742.77</v>
+        <v>-336427478.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>515211246.21</v>
+        <v>354899239</v>
       </c>
       <c r="AB4" t="n">
-        <v>-213656534.81</v>
+        <v>-367851973.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>5313590.3</v>
+        <v>13767604.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>-357859477.25</v>
+        <v>-33161906.92</v>
       </c>
       <c r="AE4" t="n">
-        <v>130370407.84</v>
+        <v>-44983277.37</v>
       </c>
       <c r="AF4" t="n">
-        <v>8518944.300000001</v>
+        <v>-303474394.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>58620765.03</v>
+        <v>48823209.92</v>
       </c>
       <c r="AH4" t="n">
-        <v>428877492.75</v>
+        <v>497920655.13</v>
       </c>
       <c r="AI4" t="n">
-        <v>11795385.66</v>
+        <v>12957099.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>417082107.09</v>
+        <v>484963555.43</v>
       </c>
       <c r="AK4" t="n">
-        <v>-132769499.64</v>
+        <v>-49952416.01</v>
       </c>
       <c r="AL4" t="n">
-        <v>-133096023.69</v>
+        <v>-4896781.32</v>
       </c>
       <c r="AM4" t="n">
-        <v>339652728.96</v>
+        <v>181186020.52</v>
       </c>
       <c r="AN4" t="n">
-        <v>515211246.21</v>
+        <v>354899239</v>
       </c>
       <c r="AO4" t="n">
-        <v>77146926.73</v>
+        <v>-53015227.81</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2928041548.77</v>
+        <v>-3758598952.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-322826031.62</v>
+        <v>-268061972.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1037722795.24</v>
+        <v>-924909862.21</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1567492721.91</v>
+        <v>-2565627118.11</v>
       </c>
       <c r="AT4" t="n">
-        <v>3366105868.25</v>
+        <v>4166513419.73</v>
       </c>
       <c r="AU4" t="n">
-        <v>461718809.12</v>
+        <v>382677150.91</v>
       </c>
       <c r="AV4" t="n">
-        <v>2904387059.13</v>
+        <v>3783836268.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1571442330.07</v>
+        <v>155297146.34</v>
       </c>
       <c r="C5" t="n">
-        <v>-520964184.78</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1170294618.99</v>
-      </c>
+        <v>-35178777.53</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>-2206144367.97</v>
+        <v>-297483706.83</v>
       </c>
       <c r="F5" t="n">
-        <v>1205780995.63</v>
+        <v>4326490779.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1951850750.27</v>
+        <v>4249529974.51</v>
       </c>
       <c r="H5" t="n">
-        <v>-1523748.42</v>
+        <v>5470277.19</v>
       </c>
       <c r="I5" t="n">
-        <v>-744546006.22</v>
+        <v>71490528.11</v>
       </c>
       <c r="J5" t="n">
-        <v>637797692.3</v>
+        <v>-110163148.69</v>
       </c>
       <c r="K5" t="n">
-        <v>68752688.77</v>
+        <v>-3370589.34</v>
       </c>
       <c r="L5" t="n">
-        <v>-78486430.68000001</v>
+        <v>-67445941.81999999</v>
       </c>
       <c r="M5" t="n">
-        <v>649330434.21</v>
+        <v>-35178777.53</v>
       </c>
       <c r="N5" t="n">
-        <v>649330434.21</v>
+        <v>-35178777.53</v>
       </c>
       <c r="O5" t="n">
-        <v>-520964184.78</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1170294618.99</v>
-      </c>
+        <v>-35178777.53</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-2017045736.42</v>
-      </c>
-      <c r="R5" t="n">
-        <v>89977546.31999999</v>
-      </c>
+        <v>-271127176.37</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>35163485.23</v>
+        <v>5228761.01</v>
       </c>
       <c r="T5" t="n">
-        <v>68048488.83</v>
+        <v>224228761.01</v>
       </c>
       <c r="U5" t="n">
-        <v>-32885003.6</v>
+        <v>-219000000</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-2142186767.97</v>
+        <v>-276355937.38</v>
       </c>
       <c r="Y5" t="n">
-        <v>63957600</v>
+        <v>21127769.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2206144367.97</v>
+        <v>-297483706.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>634702037.9</v>
+        <v>452780853.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>-568734241.11</v>
+        <v>-588167051.3099999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1392298.62</v>
+        <v>17124168.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>-129699897.17</v>
+        <v>215253323.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>-456273551.77</v>
+        <v>-354189916.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>18631506.45</v>
+        <v>-466354626.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>68754482.03</v>
+        <v>41806776.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>326121666.87</v>
+        <v>616451086.4299999</v>
       </c>
       <c r="AI5" t="n">
-        <v>8032620.82</v>
+        <v>15436939.76</v>
       </c>
       <c r="AJ5" t="n">
-        <v>318089046.05</v>
+        <v>601014146.67</v>
       </c>
       <c r="AK5" t="n">
-        <v>-124194909.24</v>
+        <v>-58126767.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>-50676382.36</v>
+        <v>-253048.75</v>
       </c>
       <c r="AM5" t="n">
-        <v>950902158.0599999</v>
+        <v>330947413.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>634702037.9</v>
+        <v>452780853.17</v>
       </c>
       <c r="AO5" t="n">
-        <v>-273929661.28</v>
+        <v>-181066459.06</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3312506972.09</v>
+        <v>-3964318422.28</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-256101176.97</v>
+        <v>-187682535.04</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1069809172.5</v>
+        <v>-1074252450.28</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1986596622.62</v>
+        <v>-2702383436.96</v>
       </c>
       <c r="AT5" t="n">
-        <v>4221138671.27</v>
+        <v>4598165734.51</v>
       </c>
       <c r="AU5" t="n">
-        <v>364982469.07</v>
+        <v>263198722.54</v>
       </c>
       <c r="AV5" t="n">
-        <v>3856156202.2</v>
+        <v>4334967011.97</v>
       </c>
     </row>
   </sheetData>
@@ -4062,142 +4062,142 @@
       </c>
       <c r="DP1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
         </is>
       </c>
       <c r="ER1" t="inlineStr">
@@ -4302,34 +4302,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>48.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>36.89</v>
+        <v>71.5</v>
       </c>
       <c r="W2" t="n">
-        <v>49.55</v>
+        <v>70.33</v>
       </c>
       <c r="X2" t="n">
-        <v>53.5</v>
+        <v>75.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>48.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>36.89</v>
+        <v>71.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>49.55</v>
+        <v>70.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>53.5</v>
+        <v>75.75</v>
       </c>
       <c r="AC2" t="n">
         <v>0.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="AE2" t="n">
         <v>1752192000</v>
@@ -4341,67 +4341,67 @@
         <v>0.74</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.284</v>
+        <v>1.816</v>
       </c>
       <c r="AI2" t="n">
-        <v>196.4074</v>
+        <v>270.2963</v>
       </c>
       <c r="AJ2" t="n">
-        <v>101.980774</v>
+        <v>140.34616</v>
       </c>
       <c r="AK2" t="n">
-        <v>229543395</v>
+        <v>156696183</v>
       </c>
       <c r="AL2" t="n">
-        <v>229543395</v>
+        <v>156696183</v>
       </c>
       <c r="AM2" t="n">
-        <v>86019254</v>
+        <v>105589238</v>
       </c>
       <c r="AN2" t="n">
-        <v>139571526</v>
+        <v>169508529</v>
       </c>
       <c r="AO2" t="n">
-        <v>139571526</v>
+        <v>169508529</v>
       </c>
       <c r="AP2" t="n">
-        <v>53.24</v>
+        <v>72.81</v>
       </c>
       <c r="AQ2" t="n">
-        <v>53.25</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>61356412928</v>
+        <v>84438827008</v>
       </c>
       <c r="AS2" t="n">
-        <v>61356410579</v>
+        <v>86313185540</v>
       </c>
       <c r="AT2" t="n">
         <v>12.91</v>
       </c>
       <c r="AU2" t="n">
-        <v>53.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>53.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AW2" t="n">
         <v>1.069958</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.230886</v>
+        <v>14.079767</v>
       </c>
       <c r="AY2" t="n">
-        <v>26.0012</v>
+        <v>38.1908</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.92515</v>
+        <v>23.28315</v>
       </c>
       <c r="BA2" t="n">
         <v>0.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0020559211</v>
+        <v>0.0013404826</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>57188175872</v>
+        <v>80080609280</v>
       </c>
       <c r="BF2" t="n">
         <v>0.05124</v>
@@ -4427,7 +4427,7 @@
         <v>0.30825</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.105349995</v>
+        <v>0.105340004</v>
       </c>
       <c r="BK2" t="n">
         <v>1157013211</v>
@@ -4436,7 +4436,7 @@
         <v>10.878</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.8749766</v>
+        <v>6.708954</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4468,16 +4468,16 @@
         <v>1144281600</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.536</v>
+        <v>13.353</v>
       </c>
       <c r="BX2" t="n">
-        <v>65.55</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.0052872</v>
+        <v>4.6558</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.15</v>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>53.03</v>
+        <v>72.98</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="DH2" t="n">
-        <v>1780038246</v>
+        <v>1782111867</v>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
@@ -4632,101 +4632,101 @@
       <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="n">
-        <v>9.025493000000001</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>53.03</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Guangdong Fenghua Advanced Technology (Holding) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>FENGHUA ADVANCE TECHNOLOGY HLDG</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Guangdong Fenghua Advanced Technology (Holding) Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>849231000000</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-1.6199951</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>70.33 - 75.75</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>105589238</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>60.070004</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>4.6529827</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>12.91 - 76.1</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-3.119995</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.040998623</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>465.58</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1651229940</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1651492800</v>
+      </c>
+      <c r="EF2" t="n">
         <v>0.27</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EG2" t="n">
         <v>0.52</v>
       </c>
-      <c r="DW2" t="n">
-        <v>27.0288</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1.0395212</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>33.10485</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1.6614605</v>
-      </c>
-      <c r="EA2" t="n">
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>34.789204</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.9109315</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>49.696854</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>2.1344557</v>
+      </c>
+      <c r="EM2" t="n">
         <v>15</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="EN2" t="n">
         <v>15</v>
       </c>
-      <c r="EC2" t="b">
+      <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>849231000000</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>4.3899994</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>49.55 - 53.5</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>86019254</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>3.1076684</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>12.91 - 53.5</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.47000122</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.008785070000000001</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>300.52872</v>
-      </c>
       <c r="EP2" t="n">
-        <v>1651229940</v>
+        <v>-2.1715753</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1651492800</v>
+        <v>72.98</v>
       </c>
       <c r="ER2" t="inlineStr"/>
     </row>
